--- a/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
+++ b/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
@@ -16,10 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);-"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,13 +41,17 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="9"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="000000FF"/>
-      <sz val="9"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -62,17 +67,19 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -80,8 +87,13 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F7FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -145,46 +162,60 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -568,6 +599,10 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -587,1735 +622,2210 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Отбор: статус «активен», выплаты продолжаются в 2026. Внутри каждого ЮЛ: по стажу (лет выплат) по убыванию, далее по общей сумме по убыванию.</t>
+          <t>Отбор: статус «активен», выплаты продолжаются в 2026. Внутри каждого ЮЛ: по стажу по убыванию, далее по общей сумме по убыванию.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Выплат в 2026 (мес.):</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+          <t>ДОПУЩЕНИЯ (синие ячейки — можно менять, всё пересчитается):</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Выплат в 2026 (мес.)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>← допущение: в 2026 прошло 7 выплат (16.01, 13.02, 13.03, 15.04, 15.05, 15.06, 15.07)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>← 16.01, 13.02, 13.03, 15.04, 15.05, 15.06, 15.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Комиссия платформы 4dev</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>← начисляется сверху на среднемесячную</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Сбор ЮЛ Сингапура</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>← среднемесячная делится на (1 − ставка) = 0,975</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Ставка НПД</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>← начисляется сверху на среднемесячную</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>ФИО</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Проект</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>ЮЛ</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Ставка НПД</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Период выплат</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Лет</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="N10" s="7" t="inlineStr">
         <is>
           <t>Итого 2022–2026</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>Среднемес. выплата 2026</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>Комиссия 4dev 3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>Со сбором ЮЛ Сингапур (÷0,975)</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>С НПД +6%</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>ИТОГО к оплате в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>БВ — 15 чел.</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Глубокая Яна Ярославовна</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H12" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I12" s="12" t="n">
         <v>74734</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J12" s="12" t="n">
         <v>1277373</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K12" s="12" t="n">
         <v>2001199</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L12" s="12" t="n">
         <v>2541224</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M12" s="12" t="n">
         <v>1468449.18</v>
       </c>
-      <c r="N8" s="11">
-        <f>SUM(I8:M8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="12">
-        <f>M8/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="N12" s="13">
+        <f>SUM(I12:M12)</f>
+        <v/>
+      </c>
+      <c r="O12" s="13">
+        <f>M12/$C$5</f>
+        <v/>
+      </c>
+      <c r="P12" s="14">
+        <f>O12*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q12" s="14">
+        <f>O12/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R12" s="14">
+        <f>O12*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S12" s="15">
+        <f>O12/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Высочинский Даниил Сергеевич</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H9" s="8" t="n">
+      <c r="H13" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="I9" s="10" t="n">
+      <c r="I13" s="18" t="n">
         <v>43489</v>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="J13" s="18" t="n">
         <v>715306.13</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K13" s="18" t="n">
         <v>1582317</v>
       </c>
-      <c r="L9" s="10" t="n">
+      <c r="L13" s="18" t="n">
         <v>1778297</v>
       </c>
-      <c r="M9" s="10" t="n">
+      <c r="M13" s="18" t="n">
         <v>1146293</v>
       </c>
-      <c r="N9" s="11">
-        <f>SUM(I9:M9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="12">
-        <f>M9/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="n">
+      <c r="N13" s="19">
+        <f>SUM(I13:M13)</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>M13/$C$5</f>
+        <v/>
+      </c>
+      <c r="P13" s="20">
+        <f>O13*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q13" s="20">
+        <f>O13/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R13" s="20">
+        <f>O13*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S13" s="21">
+        <f>O13/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Дроздова Мария Глебовна</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="H14" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I14" s="12" t="n">
         <v>41064</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J14" s="12" t="n">
         <v>637553</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K14" s="12" t="n">
         <v>1442457</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L14" s="12" t="n">
         <v>1784722</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M14" s="12" t="n">
         <v>1222167</v>
       </c>
-      <c r="N10" s="11">
-        <f>SUM(I10:M10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="12">
-        <f>M10/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
+      <c r="N14" s="13">
+        <f>SUM(I14:M14)</f>
+        <v/>
+      </c>
+      <c r="O14" s="13">
+        <f>M14/$C$5</f>
+        <v/>
+      </c>
+      <c r="P14" s="14">
+        <f>O14*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q14" s="14">
+        <f>O14/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R14" s="14">
+        <f>O14*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S14" s="15">
+        <f>O14/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Кузьмина Елена Игоревна</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G15" s="16" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H15" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I15" s="18" t="n">
         <v>59574</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J15" s="18" t="n">
         <v>100638</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K15" s="18" t="n">
         <v>1253297</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L15" s="18" t="n">
         <v>115745</v>
       </c>
-      <c r="M11" s="10" t="n">
+      <c r="M15" s="18" t="n">
         <v>1062722</v>
       </c>
-      <c r="N11" s="11">
-        <f>SUM(I11:M11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="12">
-        <f>M11/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="N15" s="19">
+        <f>SUM(I15:M15)</f>
+        <v/>
+      </c>
+      <c r="O15" s="19">
+        <f>M15/$C$5</f>
+        <v/>
+      </c>
+      <c r="P15" s="20">
+        <f>O15*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q15" s="20">
+        <f>O15/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R15" s="20">
+        <f>O15*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S15" s="21">
+        <f>O15/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Гатиатуллина Марина Эдуардовна</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Fansy</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H16" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J16" s="12" t="n">
         <v>269105.17</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K16" s="12" t="n">
         <v>1743298</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L16" s="12" t="n">
         <v>1991245.01</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M16" s="12" t="n">
         <v>1192011.1</v>
       </c>
-      <c r="N12" s="11">
-        <f>SUM(I12:M12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="12">
-        <f>M12/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
+      <c r="N16" s="13">
+        <f>SUM(I16:M16)</f>
+        <v/>
+      </c>
+      <c r="O16" s="13">
+        <f>M16/$C$5</f>
+        <v/>
+      </c>
+      <c r="P16" s="14">
+        <f>O16*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q16" s="14">
+        <f>O16/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R16" s="14">
+        <f>O16*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S16" s="15">
+        <f>O16/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Оглезнева Полина Сергеевна</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H17" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="10" t="n">
+      <c r="I17" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="J17" s="18" t="n">
         <v>140852</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K17" s="18" t="n">
         <v>205851</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L17" s="18" t="n">
         <v>2326991</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M17" s="18" t="n">
         <v>1574518</v>
       </c>
-      <c r="N13" s="11">
-        <f>SUM(I13:M13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="12">
-        <f>M13/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="n">
+      <c r="N17" s="19">
+        <f>SUM(I17:M17)</f>
+        <v/>
+      </c>
+      <c r="O17" s="19">
+        <f>M17/$C$5</f>
+        <v/>
+      </c>
+      <c r="P17" s="20">
+        <f>O17*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q17" s="20">
+        <f>O17/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R17" s="20">
+        <f>O17*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S17" s="21">
+        <f>O17/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Бобрышева Татьяна Сергеевна</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="10" t="n">
+      <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="J18" s="12" t="n">
         <v>554372.52</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="K18" s="12" t="n">
         <v>1016796.76</v>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="L18" s="12" t="n">
         <v>1505710.52</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="M18" s="12" t="n">
         <v>1082430.98</v>
       </c>
-      <c r="N14" s="11">
-        <f>SUM(I14:M14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="12">
-        <f>M14/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="N18" s="13">
+        <f>SUM(I18:M18)</f>
+        <v/>
+      </c>
+      <c r="O18" s="13">
+        <f>M18/$C$5</f>
+        <v/>
+      </c>
+      <c r="P18" s="14">
+        <f>O18*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q18" s="14">
+        <f>O18/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R18" s="14">
+        <f>O18*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S18" s="15">
+        <f>O18/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Абдуллина Аделина Линаровна</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C19" s="17" t="inlineStr">
         <is>
           <t>Fansy</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H15" s="8" t="n">
+      <c r="H19" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="10" t="n">
+      <c r="I19" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="J19" s="18" t="n">
         <v>129104.22</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="K19" s="18" t="n">
         <v>690632</v>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="L19" s="18" t="n">
         <v>1072320</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="M19" s="18" t="n">
         <v>755000</v>
       </c>
-      <c r="N15" s="11">
-        <f>SUM(I15:M15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="12">
-        <f>M15/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="n">
+      <c r="N19" s="19">
+        <f>SUM(I19:M19)</f>
+        <v/>
+      </c>
+      <c r="O19" s="19">
+        <f>M19/$C$5</f>
+        <v/>
+      </c>
+      <c r="P19" s="20">
+        <f>O19*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q19" s="20">
+        <f>O19/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R19" s="20">
+        <f>O19*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S19" s="21">
+        <f>O19/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Демакова Дарья</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>ТХ</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="10" t="n">
+      <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="J20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K20" s="12" t="n">
         <v>582823.1800000001</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L20" s="12" t="n">
         <v>1530724</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M20" s="12" t="n">
         <v>1167329</v>
       </c>
-      <c r="N16" s="11">
-        <f>SUM(I16:M16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="12">
-        <f>M16/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
+      <c r="N20" s="13">
+        <f>SUM(I20:M20)</f>
+        <v/>
+      </c>
+      <c r="O20" s="13">
+        <f>M20/$C$5</f>
+        <v/>
+      </c>
+      <c r="P20" s="14">
+        <f>O20*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q20" s="14">
+        <f>O20/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R20" s="14">
+        <f>O20*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S20" s="15">
+        <f>O20/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Кузнецова Светлана Дмитриевна</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D21" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E21" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G21" s="16" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H21" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="10" t="n">
+      <c r="I21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="J21" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="10" t="n">
+      <c r="K21" s="18" t="n">
         <v>1425506.19</v>
       </c>
-      <c r="L17" s="10" t="n">
+      <c r="L21" s="18" t="n">
         <v>109043</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M21" s="18" t="n">
         <v>1145357.79</v>
       </c>
-      <c r="N17" s="11">
-        <f>SUM(I17:M17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="12">
-        <f>M17/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="n">
+      <c r="N21" s="19">
+        <f>SUM(I21:M21)</f>
+        <v/>
+      </c>
+      <c r="O21" s="19">
+        <f>M21/$C$5</f>
+        <v/>
+      </c>
+      <c r="P21" s="20">
+        <f>O21*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q21" s="20">
+        <f>O21/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R21" s="20">
+        <f>O21*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S21" s="21">
+        <f>O21/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Нуруллина Анжелика Альбертовна</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Fansy</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H18" s="8" t="n">
+      <c r="H22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="10" t="n">
+      <c r="I22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="10" t="n">
+      <c r="J22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="K22" s="12" t="n">
         <v>338830</v>
       </c>
-      <c r="L18" s="10" t="n">
+      <c r="L22" s="12" t="n">
         <v>1331065</v>
       </c>
-      <c r="M18" s="10" t="n">
+      <c r="M22" s="12" t="n">
         <v>741701</v>
       </c>
-      <c r="N18" s="11">
-        <f>SUM(I18:M18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="12">
-        <f>M18/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
+      <c r="N22" s="13">
+        <f>SUM(I22:M22)</f>
+        <v/>
+      </c>
+      <c r="O22" s="13">
+        <f>M22/$C$5</f>
+        <v/>
+      </c>
+      <c r="P22" s="14">
+        <f>O22*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q22" s="14">
+        <f>O22/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R22" s="14">
+        <f>O22*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S22" s="15">
+        <f>O22/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Тупико Олег Николаевич</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>ГК (общие)</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G23" s="16" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H23" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="10" t="n">
+      <c r="I23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="10" t="n">
+      <c r="J23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="10" t="n">
+      <c r="K23" s="18" t="n">
         <v>259907</v>
       </c>
-      <c r="L19" s="10" t="n">
+      <c r="L23" s="18" t="n">
         <v>337036</v>
       </c>
-      <c r="M19" s="10" t="n">
+      <c r="M23" s="18" t="n">
         <v>1219304</v>
       </c>
-      <c r="N19" s="11">
-        <f>SUM(I19:M19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="12">
-        <f>M19/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="n">
+      <c r="N23" s="19">
+        <f>SUM(I23:M23)</f>
+        <v/>
+      </c>
+      <c r="O23" s="19">
+        <f>M23/$C$5</f>
+        <v/>
+      </c>
+      <c r="P23" s="20">
+        <f>O23*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q23" s="20">
+        <f>O23/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R23" s="20">
+        <f>O23*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S23" s="21">
+        <f>O23/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Лукьянова Вера Константиновна</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H24" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="10" t="n">
+      <c r="J24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="10" t="n">
+      <c r="K24" s="12" t="n">
         <v>141702</v>
       </c>
-      <c r="L20" s="10" t="n">
+      <c r="L24" s="12" t="n">
         <v>73617</v>
       </c>
-      <c r="M20" s="10" t="n">
+      <c r="M24" s="12" t="n">
         <v>973404</v>
       </c>
-      <c r="N20" s="11">
-        <f>SUM(I20:M20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="12">
-        <f>M20/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
+      <c r="N24" s="13">
+        <f>SUM(I24:M24)</f>
+        <v/>
+      </c>
+      <c r="O24" s="13">
+        <f>M24/$C$5</f>
+        <v/>
+      </c>
+      <c r="P24" s="14">
+        <f>O24*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q24" s="14">
+        <f>O24/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R24" s="14">
+        <f>O24*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S24" s="15">
+        <f>O24/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Левашева Анна Алексеевна</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D25" s="16" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E25" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F25" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G25" s="16" t="inlineStr">
         <is>
           <t>2025–2026</t>
         </is>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H25" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="10" t="n">
+      <c r="J25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="10" t="n">
+      <c r="K25" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="10" t="n">
+      <c r="L25" s="18" t="n">
         <v>798831.01</v>
       </c>
-      <c r="M21" s="10" t="n">
+      <c r="M25" s="18" t="n">
         <v>1362100.09</v>
       </c>
-      <c r="N21" s="11">
-        <f>SUM(I21:M21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="12">
-        <f>M21/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="n">
+      <c r="N25" s="19">
+        <f>SUM(I25:M25)</f>
+        <v/>
+      </c>
+      <c r="O25" s="19">
+        <f>M25/$C$5</f>
+        <v/>
+      </c>
+      <c r="P25" s="20">
+        <f>O25*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q25" s="20">
+        <f>O25/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R25" s="20">
+        <f>O25*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S25" s="21">
+        <f>O25/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Капустина Вероника Сергеевна</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ОСК)</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>2025–2026</t>
         </is>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="10" t="n">
+      <c r="I26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="J26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="10" t="n">
+      <c r="K26" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="10" t="n">
+      <c r="L26" s="12" t="n">
         <v>214440.3</v>
       </c>
-      <c r="M22" s="10" t="n">
+      <c r="M26" s="12" t="n">
         <v>1228052.73</v>
       </c>
-      <c r="N22" s="11">
-        <f>SUM(I22:M22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="12">
-        <f>M22/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="N26" s="13">
+        <f>SUM(I26:M26)</f>
+        <v/>
+      </c>
+      <c r="O26" s="13">
+        <f>M26/$C$5</f>
+        <v/>
+      </c>
+      <c r="P26" s="14">
+        <f>O26*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q26" s="14">
+        <f>O26/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R26" s="14">
+        <f>O26*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S26" s="15">
+        <f>O26/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n"/>
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>Итого БВ</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="13" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="15">
-        <f>SUM(I8:I22)</f>
-        <v/>
-      </c>
-      <c r="J23" s="15">
-        <f>SUM(J8:J22)</f>
-        <v/>
-      </c>
-      <c r="K23" s="15">
-        <f>SUM(K8:K22)</f>
-        <v/>
-      </c>
-      <c r="L23" s="15">
-        <f>SUM(L8:L22)</f>
-        <v/>
-      </c>
-      <c r="M23" s="15">
-        <f>SUM(M8:M22)</f>
-        <v/>
-      </c>
-      <c r="N23" s="15">
-        <f>SUM(N8:N22)</f>
-        <v/>
-      </c>
-      <c r="O23" s="15">
-        <f>SUM(O8:O22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="24">
+        <f>SUM(I12:I26)</f>
+        <v/>
+      </c>
+      <c r="J27" s="24">
+        <f>SUM(J12:J26)</f>
+        <v/>
+      </c>
+      <c r="K27" s="24">
+        <f>SUM(K12:K26)</f>
+        <v/>
+      </c>
+      <c r="L27" s="24">
+        <f>SUM(L12:L26)</f>
+        <v/>
+      </c>
+      <c r="M27" s="24">
+        <f>SUM(M12:M26)</f>
+        <v/>
+      </c>
+      <c r="N27" s="24">
+        <f>SUM(N12:N26)</f>
+        <v/>
+      </c>
+      <c r="O27" s="24">
+        <f>SUM(O12:O26)</f>
+        <v/>
+      </c>
+      <c r="P27" s="24">
+        <f>SUM(P12:P26)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="24">
+        <f>SUM(Q12:Q26)</f>
+        <v/>
+      </c>
+      <c r="R27" s="24">
+        <f>SUM(R12:R26)</f>
+        <v/>
+      </c>
+      <c r="S27" s="24">
+        <f>SUM(S12:S26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>АС — 4 чел.</t>
         </is>
       </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="7" t="n"/>
-      <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n"/>
-      <c r="O25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="n">
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="9" t="n"/>
+      <c r="M29" s="9" t="n"/>
+      <c r="N29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
+      <c r="P29" s="9" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Грудинин Алексей Сергеевич</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H30" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I26" s="10" t="n">
+      <c r="I30" s="12" t="n">
         <v>267577.88</v>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="J30" s="12" t="n">
         <v>960405.97</v>
       </c>
-      <c r="K26" s="10" t="n">
+      <c r="K30" s="12" t="n">
         <v>1372957.36</v>
       </c>
-      <c r="L26" s="10" t="n">
+      <c r="L30" s="12" t="n">
         <v>1558585.08</v>
       </c>
-      <c r="M26" s="10" t="n">
+      <c r="M30" s="12" t="n">
         <v>938053.12</v>
       </c>
-      <c r="N26" s="11">
-        <f>SUM(I26:M26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="12">
-        <f>M26/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
+      <c r="N30" s="13">
+        <f>SUM(I30:M30)</f>
+        <v/>
+      </c>
+      <c r="O30" s="13">
+        <f>M30/$C$5</f>
+        <v/>
+      </c>
+      <c r="P30" s="14">
+        <f>O30*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q30" s="14">
+        <f>O30/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R30" s="14">
+        <f>O30*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S30" s="15">
+        <f>O30/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Репетенко Инна Эдуардовна</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ОРБ)</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D31" s="16" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E31" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F31" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G31" s="16" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H31" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="I27" s="10" t="n">
+      <c r="I31" s="18" t="n">
         <v>112190</v>
       </c>
-      <c r="J27" s="10" t="n">
+      <c r="J31" s="18" t="n">
         <v>246600</v>
       </c>
-      <c r="K27" s="10" t="n">
+      <c r="K31" s="18" t="n">
         <v>415655.93</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L31" s="18" t="n">
         <v>142973.52</v>
       </c>
-      <c r="M27" s="10" t="n">
+      <c r="M31" s="18" t="n">
         <v>905821.35</v>
       </c>
-      <c r="N27" s="11">
-        <f>SUM(I27:M27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="12">
-        <f>M27/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="n">
+      <c r="N31" s="19">
+        <f>SUM(I31:M31)</f>
+        <v/>
+      </c>
+      <c r="O31" s="19">
+        <f>M31/$C$5</f>
+        <v/>
+      </c>
+      <c r="P31" s="20">
+        <f>O31*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q31" s="20">
+        <f>O31/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R31" s="20">
+        <f>O31*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S31" s="21">
+        <f>O31/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>Жиркова Валентина Александровна</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H32" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="J32" s="12" t="n">
         <v>257222.24</v>
       </c>
-      <c r="K28" s="10" t="n">
+      <c r="K32" s="12" t="n">
         <v>1497661</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L32" s="12" t="n">
         <v>2201639.5</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M32" s="12" t="n">
         <v>1656517.19</v>
       </c>
-      <c r="N28" s="11">
-        <f>SUM(I28:M28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="12">
-        <f>M28/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
+      <c r="N32" s="13">
+        <f>SUM(I32:M32)</f>
+        <v/>
+      </c>
+      <c r="O32" s="13">
+        <f>M32/$C$5</f>
+        <v/>
+      </c>
+      <c r="P32" s="14">
+        <f>O32*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q32" s="14">
+        <f>O32/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R32" s="14">
+        <f>O32*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S32" s="15">
+        <f>O32/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Возмищева Ксения Дмитриевна</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>ТФМ (ОРБ)</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G33" s="16" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H33" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="10" t="n">
+      <c r="I33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="J33" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="10" t="n">
+      <c r="K33" s="18" t="n">
         <v>333311.66</v>
       </c>
-      <c r="L29" s="10" t="n">
+      <c r="L33" s="18" t="n">
         <v>1347175.74</v>
       </c>
-      <c r="M29" s="10" t="n">
+      <c r="M33" s="18" t="n">
         <v>1267879.25</v>
       </c>
-      <c r="N29" s="11">
-        <f>SUM(I29:M29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="12">
-        <f>M29/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="n"/>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="N33" s="19">
+        <f>SUM(I33:M33)</f>
+        <v/>
+      </c>
+      <c r="O33" s="19">
+        <f>M33/$C$5</f>
+        <v/>
+      </c>
+      <c r="P33" s="20">
+        <f>O33*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q33" s="20">
+        <f>O33/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R33" s="20">
+        <f>O33*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S33" s="21">
+        <f>O33/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n"/>
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Итого АС</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="13" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="15">
-        <f>SUM(I26:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="15">
-        <f>SUM(J26:J29)</f>
-        <v/>
-      </c>
-      <c r="K30" s="15">
-        <f>SUM(K26:K29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="15">
-        <f>SUM(L26:L29)</f>
-        <v/>
-      </c>
-      <c r="M30" s="15">
-        <f>SUM(M26:M29)</f>
-        <v/>
-      </c>
-      <c r="N30" s="15">
-        <f>SUM(N26:N29)</f>
-        <v/>
-      </c>
-      <c r="O30" s="15">
-        <f>SUM(O26:O29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="24">
+        <f>SUM(I30:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="24">
+        <f>SUM(J30:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="24">
+        <f>SUM(K30:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="24">
+        <f>SUM(L30:L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="24">
+        <f>SUM(M30:M33)</f>
+        <v/>
+      </c>
+      <c r="N34" s="24">
+        <f>SUM(N30:N33)</f>
+        <v/>
+      </c>
+      <c r="O34" s="24">
+        <f>SUM(O30:O33)</f>
+        <v/>
+      </c>
+      <c r="P34" s="24">
+        <f>SUM(P30:P33)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="24">
+        <f>SUM(Q30:Q33)</f>
+        <v/>
+      </c>
+      <c r="R34" s="24">
+        <f>SUM(R30:R33)</f>
+        <v/>
+      </c>
+      <c r="S34" s="24">
+        <f>SUM(S30:S33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ИП МТ — 1 чел.</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
-      <c r="I32" s="7" t="n"/>
-      <c r="J32" s="7" t="n"/>
-      <c r="K32" s="7" t="n"/>
-      <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
-      <c r="N32" s="7" t="n"/>
-      <c r="O32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="9" t="n"/>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
+      <c r="P36" s="9" t="n"/>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="9" t="n"/>
+      <c r="S36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>Злобин Николай Алексеевич</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Fansy</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>ИП МТ</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G37" s="10" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H37" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="10" t="n">
+      <c r="I37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="10" t="n">
+      <c r="J37" s="12" t="n">
         <v>231383</v>
       </c>
-      <c r="K33" s="10" t="n">
+      <c r="K37" s="12" t="n">
         <v>2343163.34</v>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="L37" s="12" t="n">
         <v>2601170</v>
       </c>
-      <c r="M33" s="10" t="n">
+      <c r="M37" s="12" t="n">
         <v>1832861.81</v>
       </c>
-      <c r="N33" s="11">
-        <f>SUM(I33:M33)</f>
-        <v/>
-      </c>
-      <c r="O33" s="12">
-        <f>M33/$B$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="n"/>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="N37" s="13">
+        <f>SUM(I37:M37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="13">
+        <f>M37/$C$5</f>
+        <v/>
+      </c>
+      <c r="P37" s="14">
+        <f>O37*$C$6</f>
+        <v/>
+      </c>
+      <c r="Q37" s="14">
+        <f>O37/(1-$C$7)</f>
+        <v/>
+      </c>
+      <c r="R37" s="14">
+        <f>O37*(1+$C$8)</f>
+        <v/>
+      </c>
+      <c r="S37" s="15">
+        <f>O37/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n"/>
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>Итого ИП МТ</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="15">
-        <f>SUM(I33:I33)</f>
-        <v/>
-      </c>
-      <c r="J34" s="15">
-        <f>SUM(J33:J33)</f>
-        <v/>
-      </c>
-      <c r="K34" s="15">
-        <f>SUM(K33:K33)</f>
-        <v/>
-      </c>
-      <c r="L34" s="15">
-        <f>SUM(L33:L33)</f>
-        <v/>
-      </c>
-      <c r="M34" s="15">
-        <f>SUM(M33:M33)</f>
-        <v/>
-      </c>
-      <c r="N34" s="15">
-        <f>SUM(N33:N33)</f>
-        <v/>
-      </c>
-      <c r="O34" s="15">
-        <f>SUM(O33:O33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="n"/>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="24">
+        <f>SUM(I37:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="24">
+        <f>SUM(J37:J37)</f>
+        <v/>
+      </c>
+      <c r="K38" s="24">
+        <f>SUM(K37:K37)</f>
+        <v/>
+      </c>
+      <c r="L38" s="24">
+        <f>SUM(L37:L37)</f>
+        <v/>
+      </c>
+      <c r="M38" s="24">
+        <f>SUM(M37:M37)</f>
+        <v/>
+      </c>
+      <c r="N38" s="24">
+        <f>SUM(N37:N37)</f>
+        <v/>
+      </c>
+      <c r="O38" s="24">
+        <f>SUM(O37:O37)</f>
+        <v/>
+      </c>
+      <c r="P38" s="24">
+        <f>SUM(P37:P37)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="24">
+        <f>SUM(Q37:Q37)</f>
+        <v/>
+      </c>
+      <c r="R38" s="24">
+        <f>SUM(R37:R37)</f>
+        <v/>
+      </c>
+      <c r="S38" s="24">
+        <f>SUM(S37:S37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>ВСЕГО (20 чел.)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="18">
-        <f>I23+I30+I34</f>
-        <v/>
-      </c>
-      <c r="J36" s="18">
-        <f>J23+J30+J34</f>
-        <v/>
-      </c>
-      <c r="K36" s="18">
-        <f>K23+K30+K34</f>
-        <v/>
-      </c>
-      <c r="L36" s="18">
-        <f>L23+L30+L34</f>
-        <v/>
-      </c>
-      <c r="M36" s="18">
-        <f>M23+M30+M34</f>
-        <v/>
-      </c>
-      <c r="N36" s="18">
-        <f>N23+N30+N34</f>
-        <v/>
-      </c>
-      <c r="O36" s="18">
-        <f>O23+O30+O34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+      <c r="G40" s="25" t="n"/>
+      <c r="H40" s="25" t="n"/>
+      <c r="I40" s="27">
+        <f>I27+I34+I38</f>
+        <v/>
+      </c>
+      <c r="J40" s="27">
+        <f>J27+J34+J38</f>
+        <v/>
+      </c>
+      <c r="K40" s="27">
+        <f>K27+K34+K38</f>
+        <v/>
+      </c>
+      <c r="L40" s="27">
+        <f>L27+L34+L38</f>
+        <v/>
+      </c>
+      <c r="M40" s="27">
+        <f>M27+M34+M38</f>
+        <v/>
+      </c>
+      <c r="N40" s="27">
+        <f>N27+N34+N38</f>
+        <v/>
+      </c>
+      <c r="O40" s="27">
+        <f>O27+O34+O38</f>
+        <v/>
+      </c>
+      <c r="P40" s="27">
+        <f>P27+P34+P38</f>
+        <v/>
+      </c>
+      <c r="Q40" s="27">
+        <f>Q27+Q34+Q38</f>
+        <v/>
+      </c>
+      <c r="R40" s="27">
+        <f>R27+R34+R38</f>
+        <v/>
+      </c>
+      <c r="S40" s="27">
+        <f>S27+S34+S38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>ПЛАНИРОВАНИЕ</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Юр. лицо</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B43" s="29" t="inlineStr">
         <is>
           <t>Чел.</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C43" s="29" t="inlineStr">
         <is>
           <t>Месячный фонд</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>На 6 мес.</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E43" s="29" t="inlineStr">
         <is>
           <t>На 12 мес.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n">
+      <c r="B44" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="C40" s="23">
-        <f>O23*1</f>
-        <v/>
-      </c>
-      <c r="D40" s="23">
-        <f>O23*6</f>
-        <v/>
-      </c>
-      <c r="E40" s="23">
-        <f>O23*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="21" t="inlineStr">
+      <c r="C44" s="32">
+        <f>S27*1</f>
+        <v/>
+      </c>
+      <c r="D44" s="32">
+        <f>S27*6</f>
+        <v/>
+      </c>
+      <c r="E44" s="32">
+        <f>S27*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="B41" s="22" t="n">
+      <c r="B45" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="23">
-        <f>O30*1</f>
-        <v/>
-      </c>
-      <c r="D41" s="23">
-        <f>O30*6</f>
-        <v/>
-      </c>
-      <c r="E41" s="23">
-        <f>O30*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="C45" s="32">
+        <f>S34*1</f>
+        <v/>
+      </c>
+      <c r="D45" s="32">
+        <f>S34*6</f>
+        <v/>
+      </c>
+      <c r="E45" s="32">
+        <f>S34*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>ИП МТ</t>
         </is>
       </c>
-      <c r="B42" s="22" t="n">
+      <c r="B46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="23">
-        <f>O34*1</f>
-        <v/>
-      </c>
-      <c r="D42" s="23">
-        <f>O34*6</f>
-        <v/>
-      </c>
-      <c r="E42" s="23">
-        <f>O34*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="C46" s="32">
+        <f>S38*1</f>
+        <v/>
+      </c>
+      <c r="D46" s="32">
+        <f>S38*6</f>
+        <v/>
+      </c>
+      <c r="E46" s="32">
+        <f>S38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B43" s="25" t="n">
+      <c r="B47" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="C43" s="26">
-        <f>O36*1</f>
-        <v/>
-      </c>
-      <c r="D43" s="26">
-        <f>O36*6</f>
-        <v/>
-      </c>
-      <c r="E43" s="26">
-        <f>O36*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="C47" s="35">
+        <f>S40*1</f>
+        <v/>
+      </c>
+      <c r="D47" s="35">
+        <f>S40*6</f>
+        <v/>
+      </c>
+      <c r="E47" s="35">
+        <f>S40*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="36" t="inlineStr">
         <is>
           <t>Примечания</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>1. Данные получены через Google Drive API. Годовые итоги взяты из сводных таблиц листов; помесячные строки в выгрузке неполные.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>2. Устранено задвоение строк между листами-копиями («2023 (копия)», параллельные вкладки 2025).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>3. Столбец «Лет» — число календарных лет, в которых были выплаты. «Период выплат» — первый и последний год с выплатами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>4. Левашева и Капустина получают выплаты 2 года (2025–2026) — под критерий «более 2 лет» не подходят, включены по отдельной просьбе.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>5. Левашева — смена фамилии с 23.09.25 (Домрачева); данные до смены могут учитываться отдельно.</t>
+          <t>1. Данные получены через Google Drive API. Годовые итоги взяты из сводных таблиц листов; помесячные строки в выгрузке неполные.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>6. Ставка НПД 0% — выплаты без налога на профдоход (по данным справочника СЗ).</t>
+          <t>2. Устранено задвоение строк между листами-копиями («2023 (копия)», параллельные вкладки 2025).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>7. Среднемесячная выплата 2026 = «Итого 2026» ÷ B4 (число выплат в 2026 г.). Это фактический месячный run-rate по начислениям декабрь 2025 – июнь 2026.</t>
+          <t>3. «Лет» — число календарных лет с выплатами. «Период выплат» — первый и последний год с выплатами.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>8. Ограничение выгрузки: по фамилиям после ~«Л» ранние годы (2022–2024) могли не попасть в сводные — стаж и суммы у них могут быть занижены.</t>
+          <t>4. Среднемесячная выплата 2026 = «Итого 2026» ÷ C5. Это фактический месячный run-rate по начислениям декабрь 2025 – июнь 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>5. ВАЖНО: базовая сумма — «Итого к выплате», она УЖЕ включает НПД. Столбец «С НПД +6%» начисляет налог поверх этой суммы. Если нужен НПД на сумму «на руки», базу надо заменить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>6. «ИТОГО к оплате в месяц» = среднемесячная ÷ 0,975 × 1,06 × 1,03 (сбор ЮЛ Сингапура → НПД → комиссия 4dev).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>7. Левашева и Капустина получают выплаты 2 года (2025–2026) — под критерий «более 2 лет» не подходят, включены по отдельной просьбе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>8. Левашева — смена фамилии с 23.09.25 (Домрачева). Ставка НПД 0% в справочнике — выплаты без налога на профдоход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>9. Ограничение выгрузки: по фамилиям после ~«Л» ранние годы (2022–2024) могли не попасть в сводные — стаж и суммы у них могут быть занижены.</t>
         </is>
       </c>
     </row>

--- a/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
+++ b/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
@@ -581,7 +581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -776,12 +776,12 @@
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>Со сбором ЮЛ Сингапур (÷0,975)</t>
+          <t>Сбор ЮЛ Сингапура 2,5%</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>С НПД +6%</t>
+          <t>НПД 6%</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
@@ -880,15 +880,15 @@
         <v/>
       </c>
       <c r="Q12" s="14">
-        <f>O12/(1-$C$7)</f>
+        <f>O12/(1-$C$7)-O12</f>
         <v/>
       </c>
       <c r="R12" s="14">
-        <f>O12*(1+$C$8)</f>
+        <f>O12*$C$8</f>
         <v/>
       </c>
       <c r="S12" s="15">
-        <f>O12/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O12+P12+Q12+R12</f>
         <v/>
       </c>
     </row>
@@ -957,15 +957,15 @@
         <v/>
       </c>
       <c r="Q13" s="20">
-        <f>O13/(1-$C$7)</f>
+        <f>O13/(1-$C$7)-O13</f>
         <v/>
       </c>
       <c r="R13" s="20">
-        <f>O13*(1+$C$8)</f>
+        <f>O13*$C$8</f>
         <v/>
       </c>
       <c r="S13" s="21">
-        <f>O13/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O13+P13+Q13+R13</f>
         <v/>
       </c>
     </row>
@@ -1034,15 +1034,15 @@
         <v/>
       </c>
       <c r="Q14" s="14">
-        <f>O14/(1-$C$7)</f>
+        <f>O14/(1-$C$7)-O14</f>
         <v/>
       </c>
       <c r="R14" s="14">
-        <f>O14*(1+$C$8)</f>
+        <f>O14*$C$8</f>
         <v/>
       </c>
       <c r="S14" s="15">
-        <f>O14/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O14+P14+Q14+R14</f>
         <v/>
       </c>
     </row>
@@ -1111,15 +1111,15 @@
         <v/>
       </c>
       <c r="Q15" s="20">
-        <f>O15/(1-$C$7)</f>
+        <f>O15/(1-$C$7)-O15</f>
         <v/>
       </c>
       <c r="R15" s="20">
-        <f>O15*(1+$C$8)</f>
+        <f>O15*$C$8</f>
         <v/>
       </c>
       <c r="S15" s="21">
-        <f>O15/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O15+P15+Q15+R15</f>
         <v/>
       </c>
     </row>
@@ -1188,15 +1188,15 @@
         <v/>
       </c>
       <c r="Q16" s="14">
-        <f>O16/(1-$C$7)</f>
+        <f>O16/(1-$C$7)-O16</f>
         <v/>
       </c>
       <c r="R16" s="14">
-        <f>O16*(1+$C$8)</f>
+        <f>O16*$C$8</f>
         <v/>
       </c>
       <c r="S16" s="15">
-        <f>O16/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O16+P16+Q16+R16</f>
         <v/>
       </c>
     </row>
@@ -1265,15 +1265,15 @@
         <v/>
       </c>
       <c r="Q17" s="20">
-        <f>O17/(1-$C$7)</f>
+        <f>O17/(1-$C$7)-O17</f>
         <v/>
       </c>
       <c r="R17" s="20">
-        <f>O17*(1+$C$8)</f>
+        <f>O17*$C$8</f>
         <v/>
       </c>
       <c r="S17" s="21">
-        <f>O17/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O17+P17+Q17+R17</f>
         <v/>
       </c>
     </row>
@@ -1342,15 +1342,15 @@
         <v/>
       </c>
       <c r="Q18" s="14">
-        <f>O18/(1-$C$7)</f>
+        <f>O18/(1-$C$7)-O18</f>
         <v/>
       </c>
       <c r="R18" s="14">
-        <f>O18*(1+$C$8)</f>
+        <f>O18*$C$8</f>
         <v/>
       </c>
       <c r="S18" s="15">
-        <f>O18/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O18+P18+Q18+R18</f>
         <v/>
       </c>
     </row>
@@ -1419,15 +1419,15 @@
         <v/>
       </c>
       <c r="Q19" s="20">
-        <f>O19/(1-$C$7)</f>
+        <f>O19/(1-$C$7)-O19</f>
         <v/>
       </c>
       <c r="R19" s="20">
-        <f>O19*(1+$C$8)</f>
+        <f>O19*$C$8</f>
         <v/>
       </c>
       <c r="S19" s="21">
-        <f>O19/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O19+P19+Q19+R19</f>
         <v/>
       </c>
     </row>
@@ -1496,15 +1496,15 @@
         <v/>
       </c>
       <c r="Q20" s="14">
-        <f>O20/(1-$C$7)</f>
+        <f>O20/(1-$C$7)-O20</f>
         <v/>
       </c>
       <c r="R20" s="14">
-        <f>O20*(1+$C$8)</f>
+        <f>O20*$C$8</f>
         <v/>
       </c>
       <c r="S20" s="15">
-        <f>O20/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O20+P20+Q20+R20</f>
         <v/>
       </c>
     </row>
@@ -1573,15 +1573,15 @@
         <v/>
       </c>
       <c r="Q21" s="20">
-        <f>O21/(1-$C$7)</f>
+        <f>O21/(1-$C$7)-O21</f>
         <v/>
       </c>
       <c r="R21" s="20">
-        <f>O21*(1+$C$8)</f>
+        <f>O21*$C$8</f>
         <v/>
       </c>
       <c r="S21" s="21">
-        <f>O21/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O21+P21+Q21+R21</f>
         <v/>
       </c>
     </row>
@@ -1650,15 +1650,15 @@
         <v/>
       </c>
       <c r="Q22" s="14">
-        <f>O22/(1-$C$7)</f>
+        <f>O22/(1-$C$7)-O22</f>
         <v/>
       </c>
       <c r="R22" s="14">
-        <f>O22*(1+$C$8)</f>
+        <f>O22*$C$8</f>
         <v/>
       </c>
       <c r="S22" s="15">
-        <f>O22/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O22+P22+Q22+R22</f>
         <v/>
       </c>
     </row>
@@ -1727,15 +1727,15 @@
         <v/>
       </c>
       <c r="Q23" s="20">
-        <f>O23/(1-$C$7)</f>
+        <f>O23/(1-$C$7)-O23</f>
         <v/>
       </c>
       <c r="R23" s="20">
-        <f>O23*(1+$C$8)</f>
+        <f>O23*$C$8</f>
         <v/>
       </c>
       <c r="S23" s="21">
-        <f>O23/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O23+P23+Q23+R23</f>
         <v/>
       </c>
     </row>
@@ -1804,15 +1804,15 @@
         <v/>
       </c>
       <c r="Q24" s="14">
-        <f>O24/(1-$C$7)</f>
+        <f>O24/(1-$C$7)-O24</f>
         <v/>
       </c>
       <c r="R24" s="14">
-        <f>O24*(1+$C$8)</f>
+        <f>O24*$C$8</f>
         <v/>
       </c>
       <c r="S24" s="15">
-        <f>O24/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O24+P24+Q24+R24</f>
         <v/>
       </c>
     </row>
@@ -1881,15 +1881,15 @@
         <v/>
       </c>
       <c r="Q25" s="20">
-        <f>O25/(1-$C$7)</f>
+        <f>O25/(1-$C$7)-O25</f>
         <v/>
       </c>
       <c r="R25" s="20">
-        <f>O25*(1+$C$8)</f>
+        <f>O25*$C$8</f>
         <v/>
       </c>
       <c r="S25" s="21">
-        <f>O25/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O25+P25+Q25+R25</f>
         <v/>
       </c>
     </row>
@@ -1958,15 +1958,15 @@
         <v/>
       </c>
       <c r="Q26" s="14">
-        <f>O26/(1-$C$7)</f>
+        <f>O26/(1-$C$7)-O26</f>
         <v/>
       </c>
       <c r="R26" s="14">
-        <f>O26*(1+$C$8)</f>
+        <f>O26*$C$8</f>
         <v/>
       </c>
       <c r="S26" s="15">
-        <f>O26/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O26+P26+Q26+R26</f>
         <v/>
       </c>
     </row>
@@ -2118,15 +2118,15 @@
         <v/>
       </c>
       <c r="Q30" s="14">
-        <f>O30/(1-$C$7)</f>
+        <f>O30/(1-$C$7)-O30</f>
         <v/>
       </c>
       <c r="R30" s="14">
-        <f>O30*(1+$C$8)</f>
+        <f>O30*$C$8</f>
         <v/>
       </c>
       <c r="S30" s="15">
-        <f>O30/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O30+P30+Q30+R30</f>
         <v/>
       </c>
     </row>
@@ -2195,15 +2195,15 @@
         <v/>
       </c>
       <c r="Q31" s="20">
-        <f>O31/(1-$C$7)</f>
+        <f>O31/(1-$C$7)-O31</f>
         <v/>
       </c>
       <c r="R31" s="20">
-        <f>O31*(1+$C$8)</f>
+        <f>O31*$C$8</f>
         <v/>
       </c>
       <c r="S31" s="21">
-        <f>O31/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O31+P31+Q31+R31</f>
         <v/>
       </c>
     </row>
@@ -2272,15 +2272,15 @@
         <v/>
       </c>
       <c r="Q32" s="14">
-        <f>O32/(1-$C$7)</f>
+        <f>O32/(1-$C$7)-O32</f>
         <v/>
       </c>
       <c r="R32" s="14">
-        <f>O32*(1+$C$8)</f>
+        <f>O32*$C$8</f>
         <v/>
       </c>
       <c r="S32" s="15">
-        <f>O32/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O32+P32+Q32+R32</f>
         <v/>
       </c>
     </row>
@@ -2349,15 +2349,15 @@
         <v/>
       </c>
       <c r="Q33" s="20">
-        <f>O33/(1-$C$7)</f>
+        <f>O33/(1-$C$7)-O33</f>
         <v/>
       </c>
       <c r="R33" s="20">
-        <f>O33*(1+$C$8)</f>
+        <f>O33*$C$8</f>
         <v/>
       </c>
       <c r="S33" s="21">
-        <f>O33/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O33+P33+Q33+R33</f>
         <v/>
       </c>
     </row>
@@ -2509,15 +2509,15 @@
         <v/>
       </c>
       <c r="Q37" s="14">
-        <f>O37/(1-$C$7)</f>
+        <f>O37/(1-$C$7)-O37</f>
         <v/>
       </c>
       <c r="R37" s="14">
-        <f>O37*(1+$C$8)</f>
+        <f>O37*$C$8</f>
         <v/>
       </c>
       <c r="S37" s="15">
-        <f>O37/(1-$C$7)*(1+$C$8)*(1+$C$6)</f>
+        <f>O37+P37+Q37+R37</f>
         <v/>
       </c>
     </row>
@@ -2804,28 +2804,35 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>6. «ИТОГО к оплате в месяц» = среднемесячная ÷ 0,975 × 1,06 × 1,03 (сбор ЮЛ Сингапура → НПД → комиссия 4dev).</t>
+          <t>6. Все три надбавки считаются от среднемесячной выплаты: комиссия 4dev = ×3%; сбор ЮЛ Сингапура = ÷0,975 − среднемесячная (2,5% сверху); НПД = ×6%.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>7. Левашева и Капустина получают выплаты 2 года (2025–2026) — под критерий «более 2 лет» не подходят, включены по отдельной просьбе.</t>
+          <t>7. «ИТОГО к оплате в месяц» = среднемесячная + комиссия + сбор + НПД (надбавки не каскадируются). Если применять их последовательно (÷0,975 × 1,06 × 1,03), итог по группе будет 3 830 014 ₽ вместо 3 815 806 ₽.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>8. Левашева — смена фамилии с 23.09.25 (Домрачева). Ставка НПД 0% в справочнике — выплаты без налога на профдоход.</t>
+          <t>8. Левашева и Капустина получают выплаты 2 года (2025–2026) — под критерий «более 2 лет» не подходят, включены по отдельной просьбе.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>9. Ограничение выгрузки: по фамилиям после ~«Л» ранние годы (2022–2024) могли не попасть в сводные — стаж и суммы у них могут быть занижены.</t>
+          <t>9. Левашева — смена фамилии с 23.09.25 (Домрачева). Ставка НПД 0% в справочнике — выплаты без налога на профдоход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>10. Ограничение выгрузки: по фамилиям после ~«Л» ранние годы (2022–2024) могли не попасть в сводные — стаж и суммы у них могут быть занижены.</t>
         </is>
       </c>
     </row>

--- a/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
+++ b/СЗ_длительные_выплаты_по_ЮЛ_2022-2026.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,11 @@
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -162,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,24 +189,25 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -215,7 +221,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -581,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -603,6 +609,7 @@
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,7 +688,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ставка НПД</t>
+          <t>Ставка НПД (базовая)</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -689,7 +696,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>← начисляется сверху на среднемесячную</t>
+          <t>← фактическая ставка по каждому — в скрытом столбце T</t>
         </is>
       </c>
     </row>
@@ -766,7 +773,7 @@
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>Среднемес. выплата 2026</t>
+          <t>Среднемес. на руки 2026</t>
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
@@ -872,7 +879,7 @@
         <v/>
       </c>
       <c r="O12" s="13">
-        <f>M12/$C$5</f>
+        <f>M12/$C$5*(1-T12)</f>
         <v/>
       </c>
       <c r="P12" s="14">
@@ -884,89 +891,95 @@
         <v/>
       </c>
       <c r="R12" s="14">
-        <f>O12*$C$8</f>
+        <f>IF(T12=0,0,O12/(1-T12)-O12)</f>
         <v/>
       </c>
       <c r="S12" s="15">
         <f>O12+P12+Q12+R12</f>
         <v/>
       </c>
+      <c r="T12" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Высочинский Даниил Сергеевич</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="19" t="n">
         <v>43489</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="19" t="n">
         <v>715306.13</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K13" s="19" t="n">
         <v>1582317</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L13" s="19" t="n">
         <v>1778297</v>
       </c>
-      <c r="M13" s="18" t="n">
+      <c r="M13" s="19" t="n">
         <v>1146293</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="20">
         <f>SUM(I13:M13)</f>
         <v/>
       </c>
-      <c r="O13" s="19">
-        <f>M13/$C$5</f>
-        <v/>
-      </c>
-      <c r="P13" s="20">
+      <c r="O13" s="20">
+        <f>M13/$C$5*(1-T13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="21">
         <f>O13*$C$6</f>
         <v/>
       </c>
-      <c r="Q13" s="20">
+      <c r="Q13" s="21">
         <f>O13/(1-$C$7)-O13</f>
         <v/>
       </c>
-      <c r="R13" s="20">
-        <f>O13*$C$8</f>
-        <v/>
-      </c>
-      <c r="S13" s="21">
+      <c r="R13" s="21">
+        <f>IF(T13=0,0,O13/(1-T13)-O13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="22">
         <f>O13+P13+Q13+R13</f>
         <v/>
+      </c>
+      <c r="T13" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="14">
@@ -1026,7 +1039,7 @@
         <v/>
       </c>
       <c r="O14" s="13">
-        <f>M14/$C$5</f>
+        <f>M14/$C$5*(1-T14)</f>
         <v/>
       </c>
       <c r="P14" s="14">
@@ -1038,89 +1051,95 @@
         <v/>
       </c>
       <c r="R14" s="14">
-        <f>O14*$C$8</f>
+        <f>IF(T14=0,0,O14/(1-T14)-O14)</f>
         <v/>
       </c>
       <c r="S14" s="15">
         <f>O14+P14+Q14+R14</f>
         <v/>
       </c>
+      <c r="T14" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Кузьмина Елена Игоревна</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="19" t="n">
         <v>59574</v>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="19" t="n">
         <v>100638</v>
       </c>
-      <c r="K15" s="18" t="n">
+      <c r="K15" s="19" t="n">
         <v>1253297</v>
       </c>
-      <c r="L15" s="18" t="n">
+      <c r="L15" s="19" t="n">
         <v>115745</v>
       </c>
-      <c r="M15" s="18" t="n">
+      <c r="M15" s="19" t="n">
         <v>1062722</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="20">
         <f>SUM(I15:M15)</f>
         <v/>
       </c>
-      <c r="O15" s="19">
-        <f>M15/$C$5</f>
-        <v/>
-      </c>
-      <c r="P15" s="20">
+      <c r="O15" s="20">
+        <f>M15/$C$5*(1-T15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="21">
         <f>O15*$C$6</f>
         <v/>
       </c>
-      <c r="Q15" s="20">
+      <c r="Q15" s="21">
         <f>O15/(1-$C$7)-O15</f>
         <v/>
       </c>
-      <c r="R15" s="20">
-        <f>O15*$C$8</f>
-        <v/>
-      </c>
-      <c r="S15" s="21">
+      <c r="R15" s="21">
+        <f>IF(T15=0,0,O15/(1-T15)-O15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="22">
         <f>O15+P15+Q15+R15</f>
         <v/>
+      </c>
+      <c r="T15" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="16">
@@ -1180,7 +1199,7 @@
         <v/>
       </c>
       <c r="O16" s="13">
-        <f>M16/$C$5</f>
+        <f>M16/$C$5*(1-T16)</f>
         <v/>
       </c>
       <c r="P16" s="14">
@@ -1192,89 +1211,95 @@
         <v/>
       </c>
       <c r="R16" s="14">
-        <f>O16*$C$8</f>
+        <f>IF(T16=0,0,O16/(1-T16)-O16)</f>
         <v/>
       </c>
       <c r="S16" s="15">
         <f>O16+P16+Q16+R16</f>
         <v/>
       </c>
+      <c r="T16" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="n">
+      <c r="A17" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Оглезнева Полина Сергеевна</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ОСП)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="19" t="n">
         <v>140852</v>
       </c>
-      <c r="K17" s="18" t="n">
+      <c r="K17" s="19" t="n">
         <v>205851</v>
       </c>
-      <c r="L17" s="18" t="n">
+      <c r="L17" s="19" t="n">
         <v>2326991</v>
       </c>
-      <c r="M17" s="18" t="n">
+      <c r="M17" s="19" t="n">
         <v>1574518</v>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="20">
         <f>SUM(I17:M17)</f>
         <v/>
       </c>
-      <c r="O17" s="19">
-        <f>M17/$C$5</f>
-        <v/>
-      </c>
-      <c r="P17" s="20">
+      <c r="O17" s="20">
+        <f>M17/$C$5*(1-T17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="21">
         <f>O17*$C$6</f>
         <v/>
       </c>
-      <c r="Q17" s="20">
+      <c r="Q17" s="21">
         <f>O17/(1-$C$7)-O17</f>
         <v/>
       </c>
-      <c r="R17" s="20">
-        <f>O17*$C$8</f>
-        <v/>
-      </c>
-      <c r="S17" s="21">
+      <c r="R17" s="21">
+        <f>IF(T17=0,0,O17/(1-T17)-O17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="22">
         <f>O17+P17+Q17+R17</f>
         <v/>
+      </c>
+      <c r="T17" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="18">
@@ -1334,7 +1359,7 @@
         <v/>
       </c>
       <c r="O18" s="13">
-        <f>M18/$C$5</f>
+        <f>M18/$C$5*(1-T18)</f>
         <v/>
       </c>
       <c r="P18" s="14">
@@ -1346,89 +1371,95 @@
         <v/>
       </c>
       <c r="R18" s="14">
-        <f>O18*$C$8</f>
+        <f>IF(T18=0,0,O18/(1-T18)-O18)</f>
         <v/>
       </c>
       <c r="S18" s="15">
         <f>O18+P18+Q18+R18</f>
         <v/>
       </c>
+      <c r="T18" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Абдуллина Аделина Линаровна</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>Fansy</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>2023–2026</t>
         </is>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="19" t="n">
         <v>129104.22</v>
       </c>
-      <c r="K19" s="18" t="n">
+      <c r="K19" s="19" t="n">
         <v>690632</v>
       </c>
-      <c r="L19" s="18" t="n">
+      <c r="L19" s="19" t="n">
         <v>1072320</v>
       </c>
-      <c r="M19" s="18" t="n">
+      <c r="M19" s="19" t="n">
         <v>755000</v>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="20">
         <f>SUM(I19:M19)</f>
         <v/>
       </c>
-      <c r="O19" s="19">
-        <f>M19/$C$5</f>
-        <v/>
-      </c>
-      <c r="P19" s="20">
+      <c r="O19" s="20">
+        <f>M19/$C$5*(1-T19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="21">
         <f>O19*$C$6</f>
         <v/>
       </c>
-      <c r="Q19" s="20">
+      <c r="Q19" s="21">
         <f>O19/(1-$C$7)-O19</f>
         <v/>
       </c>
-      <c r="R19" s="20">
-        <f>O19*$C$8</f>
-        <v/>
-      </c>
-      <c r="S19" s="21">
+      <c r="R19" s="21">
+        <f>IF(T19=0,0,O19/(1-T19)-O19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="22">
         <f>O19+P19+Q19+R19</f>
         <v/>
+      </c>
+      <c r="T19" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1488,7 +1519,7 @@
         <v/>
       </c>
       <c r="O20" s="13">
-        <f>M20/$C$5</f>
+        <f>M20/$C$5*(1-T20)</f>
         <v/>
       </c>
       <c r="P20" s="14">
@@ -1500,89 +1531,95 @@
         <v/>
       </c>
       <c r="R20" s="14">
-        <f>O20*$C$8</f>
+        <f>IF(T20=0,0,O20/(1-T20)-O20)</f>
         <v/>
       </c>
       <c r="S20" s="15">
         <f>O20+P20+Q20+R20</f>
         <v/>
       </c>
+      <c r="T20" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="n">
+      <c r="A21" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Кузнецова Светлана Дмитриевна</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="18" t="n">
+      <c r="K21" s="19" t="n">
         <v>1425506.19</v>
       </c>
-      <c r="L21" s="18" t="n">
+      <c r="L21" s="19" t="n">
         <v>109043</v>
       </c>
-      <c r="M21" s="18" t="n">
+      <c r="M21" s="19" t="n">
         <v>1145357.79</v>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="20">
         <f>SUM(I21:M21)</f>
         <v/>
       </c>
-      <c r="O21" s="19">
-        <f>M21/$C$5</f>
-        <v/>
-      </c>
-      <c r="P21" s="20">
+      <c r="O21" s="20">
+        <f>M21/$C$5*(1-T21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="21">
         <f>O21*$C$6</f>
         <v/>
       </c>
-      <c r="Q21" s="20">
+      <c r="Q21" s="21">
         <f>O21/(1-$C$7)-O21</f>
         <v/>
       </c>
-      <c r="R21" s="20">
-        <f>O21*$C$8</f>
-        <v/>
-      </c>
-      <c r="S21" s="21">
+      <c r="R21" s="21">
+        <f>IF(T21=0,0,O21/(1-T21)-O21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="22">
         <f>O21+P21+Q21+R21</f>
         <v/>
+      </c>
+      <c r="T21" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="22">
@@ -1642,7 +1679,7 @@
         <v/>
       </c>
       <c r="O22" s="13">
-        <f>M22/$C$5</f>
+        <f>M22/$C$5*(1-T22)</f>
         <v/>
       </c>
       <c r="P22" s="14">
@@ -1654,89 +1691,95 @@
         <v/>
       </c>
       <c r="R22" s="14">
-        <f>O22*$C$8</f>
+        <f>IF(T22=0,0,O22/(1-T22)-O22)</f>
         <v/>
       </c>
       <c r="S22" s="15">
         <f>O22+P22+Q22+R22</f>
         <v/>
       </c>
+      <c r="T22" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="n">
+      <c r="A23" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Тупико Олег Николаевич</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>ГК (общие)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="18" t="n">
+      <c r="K23" s="19" t="n">
         <v>259907</v>
       </c>
-      <c r="L23" s="18" t="n">
+      <c r="L23" s="19" t="n">
         <v>337036</v>
       </c>
-      <c r="M23" s="18" t="n">
+      <c r="M23" s="19" t="n">
         <v>1219304</v>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="20">
         <f>SUM(I23:M23)</f>
         <v/>
       </c>
-      <c r="O23" s="19">
-        <f>M23/$C$5</f>
-        <v/>
-      </c>
-      <c r="P23" s="20">
+      <c r="O23" s="20">
+        <f>M23/$C$5*(1-T23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="21">
         <f>O23*$C$6</f>
         <v/>
       </c>
-      <c r="Q23" s="20">
+      <c r="Q23" s="21">
         <f>O23/(1-$C$7)-O23</f>
         <v/>
       </c>
-      <c r="R23" s="20">
-        <f>O23*$C$8</f>
-        <v/>
-      </c>
-      <c r="S23" s="21">
+      <c r="R23" s="21">
+        <f>IF(T23=0,0,O23/(1-T23)-O23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="22">
         <f>O23+P23+Q23+R23</f>
         <v/>
+      </c>
+      <c r="T23" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="24">
@@ -1796,7 +1839,7 @@
         <v/>
       </c>
       <c r="O24" s="13">
-        <f>M24/$C$5</f>
+        <f>M24/$C$5*(1-T24)</f>
         <v/>
       </c>
       <c r="P24" s="14">
@@ -1808,89 +1851,95 @@
         <v/>
       </c>
       <c r="R24" s="14">
-        <f>O24*$C$8</f>
+        <f>IF(T24=0,0,O24/(1-T24)-O24)</f>
         <v/>
       </c>
       <c r="S24" s="15">
         <f>O24+P24+Q24+R24</f>
         <v/>
       </c>
+      <c r="T24" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="n">
+      <c r="A25" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Левашева Анна Алексеевна</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ПО)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="17" t="inlineStr">
         <is>
           <t>2025–2026</t>
         </is>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="18" t="n">
+      <c r="K25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="L25" s="18" t="n">
+      <c r="L25" s="19" t="n">
         <v>798831.01</v>
       </c>
-      <c r="M25" s="18" t="n">
+      <c r="M25" s="19" t="n">
         <v>1362100.09</v>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="20">
         <f>SUM(I25:M25)</f>
         <v/>
       </c>
-      <c r="O25" s="19">
-        <f>M25/$C$5</f>
-        <v/>
-      </c>
-      <c r="P25" s="20">
+      <c r="O25" s="20">
+        <f>M25/$C$5*(1-T25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="21">
         <f>O25*$C$6</f>
         <v/>
       </c>
-      <c r="Q25" s="20">
+      <c r="Q25" s="21">
         <f>O25/(1-$C$7)-O25</f>
         <v/>
       </c>
-      <c r="R25" s="20">
-        <f>O25*$C$8</f>
-        <v/>
-      </c>
-      <c r="S25" s="21">
+      <c r="R25" s="21">
+        <f>IF(T25=0,0,O25/(1-T25)-O25)</f>
+        <v/>
+      </c>
+      <c r="S25" s="22">
         <f>O25+P25+Q25+R25</f>
         <v/>
+      </c>
+      <c r="T25" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
@@ -1950,7 +1999,7 @@
         <v/>
       </c>
       <c r="O26" s="13">
-        <f>M26/$C$5</f>
+        <f>M26/$C$5*(1-T26)</f>
         <v/>
       </c>
       <c r="P26" s="14">
@@ -1962,68 +2011,71 @@
         <v/>
       </c>
       <c r="R26" s="14">
-        <f>O26*$C$8</f>
+        <f>IF(T26=0,0,O26/(1-T26)-O26)</f>
         <v/>
       </c>
       <c r="S26" s="15">
         <f>O26+P26+Q26+R26</f>
         <v/>
       </c>
+      <c r="T26" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="n"/>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Итого БВ</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="22" t="n"/>
-      <c r="F27" s="22" t="n"/>
-      <c r="G27" s="22" t="n"/>
-      <c r="H27" s="22" t="n"/>
-      <c r="I27" s="24">
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="25">
         <f>SUM(I12:I26)</f>
         <v/>
       </c>
-      <c r="J27" s="24">
+      <c r="J27" s="25">
         <f>SUM(J12:J26)</f>
         <v/>
       </c>
-      <c r="K27" s="24">
+      <c r="K27" s="25">
         <f>SUM(K12:K26)</f>
         <v/>
       </c>
-      <c r="L27" s="24">
+      <c r="L27" s="25">
         <f>SUM(L12:L26)</f>
         <v/>
       </c>
-      <c r="M27" s="24">
+      <c r="M27" s="25">
         <f>SUM(M12:M26)</f>
         <v/>
       </c>
-      <c r="N27" s="24">
+      <c r="N27" s="25">
         <f>SUM(N12:N26)</f>
         <v/>
       </c>
-      <c r="O27" s="24">
+      <c r="O27" s="25">
         <f>SUM(O12:O26)</f>
         <v/>
       </c>
-      <c r="P27" s="24">
+      <c r="P27" s="25">
         <f>SUM(P12:P26)</f>
         <v/>
       </c>
-      <c r="Q27" s="24">
+      <c r="Q27" s="25">
         <f>SUM(Q12:Q26)</f>
         <v/>
       </c>
-      <c r="R27" s="24">
+      <c r="R27" s="25">
         <f>SUM(R12:R26)</f>
         <v/>
       </c>
-      <c r="S27" s="24">
+      <c r="S27" s="25">
         <f>SUM(S12:S26)</f>
         <v/>
       </c>
@@ -2110,7 +2162,7 @@
         <v/>
       </c>
       <c r="O30" s="13">
-        <f>M30/$C$5</f>
+        <f>M30/$C$5*(1-T30)</f>
         <v/>
       </c>
       <c r="P30" s="14">
@@ -2122,89 +2174,95 @@
         <v/>
       </c>
       <c r="R30" s="14">
-        <f>O30*$C$8</f>
+        <f>IF(T30=0,0,O30/(1-T30)-O30)</f>
         <v/>
       </c>
       <c r="S30" s="15">
         <f>O30+P30+Q30+R30</f>
         <v/>
       </c>
+      <c r="T30" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="n">
+      <c r="A31" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Репетенко Инна Эдуардовна</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ОРБ)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>2022–2026</t>
         </is>
       </c>
-      <c r="H31" s="16" t="n">
+      <c r="H31" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="19" t="n">
         <v>112190</v>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="19" t="n">
         <v>246600</v>
       </c>
-      <c r="K31" s="18" t="n">
+      <c r="K31" s="19" t="n">
         <v>415655.93</v>
       </c>
-      <c r="L31" s="18" t="n">
+      <c r="L31" s="19" t="n">
         <v>142973.52</v>
       </c>
-      <c r="M31" s="18" t="n">
+      <c r="M31" s="19" t="n">
         <v>905821.35</v>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="20">
         <f>SUM(I31:M31)</f>
         <v/>
       </c>
-      <c r="O31" s="19">
-        <f>M31/$C$5</f>
-        <v/>
-      </c>
-      <c r="P31" s="20">
+      <c r="O31" s="20">
+        <f>M31/$C$5*(1-T31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="21">
         <f>O31*$C$6</f>
         <v/>
       </c>
-      <c r="Q31" s="20">
+      <c r="Q31" s="21">
         <f>O31/(1-$C$7)-O31</f>
         <v/>
       </c>
-      <c r="R31" s="20">
-        <f>O31*$C$8</f>
-        <v/>
-      </c>
-      <c r="S31" s="21">
+      <c r="R31" s="21">
+        <f>IF(T31=0,0,O31/(1-T31)-O31)</f>
+        <v/>
+      </c>
+      <c r="S31" s="22">
         <f>O31+P31+Q31+R31</f>
         <v/>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="32">
@@ -2264,7 +2322,7 @@
         <v/>
       </c>
       <c r="O32" s="13">
-        <f>M32/$C$5</f>
+        <f>M32/$C$5*(1-T32)</f>
         <v/>
       </c>
       <c r="P32" s="14">
@@ -2276,145 +2334,151 @@
         <v/>
       </c>
       <c r="R32" s="14">
-        <f>O32*$C$8</f>
+        <f>IF(T32=0,0,O32/(1-T32)-O32)</f>
         <v/>
       </c>
       <c r="S32" s="15">
         <f>O32+P32+Q32+R32</f>
         <v/>
       </c>
+      <c r="T32" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="n">
+      <c r="A33" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>Возмищева Ксения Дмитриевна</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>ТФМ (ОРБ)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>активен</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>2024–2026</t>
         </is>
       </c>
-      <c r="H33" s="16" t="n">
+      <c r="H33" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="18" t="n">
+      <c r="I33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="18" t="n">
+      <c r="K33" s="19" t="n">
         <v>333311.66</v>
       </c>
-      <c r="L33" s="18" t="n">
+      <c r="L33" s="19" t="n">
         <v>1347175.74</v>
       </c>
-      <c r="M33" s="18" t="n">
+      <c r="M33" s="19" t="n">
         <v>1267879.25</v>
       </c>
-      <c r="N33" s="19">
+      <c r="N33" s="20">
         <f>SUM(I33:M33)</f>
         <v/>
       </c>
-      <c r="O33" s="19">
-        <f>M33/$C$5</f>
-        <v/>
-      </c>
-      <c r="P33" s="20">
+      <c r="O33" s="20">
+        <f>M33/$C$5*(1-T33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="21">
         <f>O33*$C$6</f>
         <v/>
       </c>
-      <c r="Q33" s="20">
+      <c r="Q33" s="21">
         <f>O33/(1-$C$7)-O33</f>
         <v/>
       </c>
-      <c r="R33" s="20">
-        <f>O33*$C$8</f>
-        <v/>
-      </c>
-      <c r="S33" s="21">
+      <c r="R33" s="21">
+        <f>IF(T33=0,0,O33/(1-T33)-O33)</f>
+        <v/>
+      </c>
+      <c r="S33" s="22">
         <f>O33+P33+Q33+R33</f>
         <v/>
       </c>
+      <c r="T33" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="n"/>
-      <c r="B34" s="23" t="inlineStr">
+      <c r="A34" s="23" t="n"/>
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Итого АС</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
-      <c r="G34" s="22" t="n"/>
-      <c r="H34" s="22" t="n"/>
-      <c r="I34" s="24">
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="23" t="n"/>
+      <c r="H34" s="23" t="n"/>
+      <c r="I34" s="25">
         <f>SUM(I30:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="24">
+      <c r="J34" s="25">
         <f>SUM(J30:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="25">
         <f>SUM(K30:K33)</f>
         <v/>
       </c>
-      <c r="L34" s="24">
+      <c r="L34" s="25">
         <f>SUM(L30:L33)</f>
         <v/>
       </c>
-      <c r="M34" s="24">
+      <c r="M34" s="25">
         <f>SUM(M30:M33)</f>
         <v/>
       </c>
-      <c r="N34" s="24">
+      <c r="N34" s="25">
         <f>SUM(N30:N33)</f>
         <v/>
       </c>
-      <c r="O34" s="24">
+      <c r="O34" s="25">
         <f>SUM(O30:O33)</f>
         <v/>
       </c>
-      <c r="P34" s="24">
+      <c r="P34" s="25">
         <f>SUM(P30:P33)</f>
         <v/>
       </c>
-      <c r="Q34" s="24">
+      <c r="Q34" s="25">
         <f>SUM(Q30:Q33)</f>
         <v/>
       </c>
-      <c r="R34" s="24">
+      <c r="R34" s="25">
         <f>SUM(R30:R33)</f>
         <v/>
       </c>
-      <c r="S34" s="24">
+      <c r="S34" s="25">
         <f>SUM(S30:S33)</f>
         <v/>
       </c>
@@ -2501,7 +2565,7 @@
         <v/>
       </c>
       <c r="O37" s="13">
-        <f>M37/$C$5</f>
+        <f>M37/$C$5*(1-T37)</f>
         <v/>
       </c>
       <c r="P37" s="14">
@@ -2513,254 +2577,257 @@
         <v/>
       </c>
       <c r="R37" s="14">
-        <f>O37*$C$8</f>
+        <f>IF(T37=0,0,O37/(1-T37)-O37)</f>
         <v/>
       </c>
       <c r="S37" s="15">
         <f>O37+P37+Q37+R37</f>
         <v/>
       </c>
+      <c r="T37" s="16" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="n"/>
-      <c r="B38" s="23" t="inlineStr">
+      <c r="A38" s="23" t="n"/>
+      <c r="B38" s="24" t="inlineStr">
         <is>
           <t>Итого ИП МТ</t>
         </is>
       </c>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
-      <c r="G38" s="22" t="n"/>
-      <c r="H38" s="22" t="n"/>
-      <c r="I38" s="24">
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="23" t="n"/>
+      <c r="F38" s="23" t="n"/>
+      <c r="G38" s="23" t="n"/>
+      <c r="H38" s="23" t="n"/>
+      <c r="I38" s="25">
         <f>SUM(I37:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="24">
+      <c r="J38" s="25">
         <f>SUM(J37:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="25">
         <f>SUM(K37:K37)</f>
         <v/>
       </c>
-      <c r="L38" s="24">
+      <c r="L38" s="25">
         <f>SUM(L37:L37)</f>
         <v/>
       </c>
-      <c r="M38" s="24">
+      <c r="M38" s="25">
         <f>SUM(M37:M37)</f>
         <v/>
       </c>
-      <c r="N38" s="24">
+      <c r="N38" s="25">
         <f>SUM(N37:N37)</f>
         <v/>
       </c>
-      <c r="O38" s="24">
+      <c r="O38" s="25">
         <f>SUM(O37:O37)</f>
         <v/>
       </c>
-      <c r="P38" s="24">
+      <c r="P38" s="25">
         <f>SUM(P37:P37)</f>
         <v/>
       </c>
-      <c r="Q38" s="24">
+      <c r="Q38" s="25">
         <f>SUM(Q37:Q37)</f>
         <v/>
       </c>
-      <c r="R38" s="24">
+      <c r="R38" s="25">
         <f>SUM(R37:R37)</f>
         <v/>
       </c>
-      <c r="S38" s="24">
+      <c r="S38" s="25">
         <f>SUM(S37:S37)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>ВСЕГО (20 чел.)</t>
         </is>
       </c>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="27">
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="26" t="n"/>
+      <c r="I40" s="28">
         <f>I27+I34+I38</f>
         <v/>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="28">
         <f>J27+J34+J38</f>
         <v/>
       </c>
-      <c r="K40" s="27">
+      <c r="K40" s="28">
         <f>K27+K34+K38</f>
         <v/>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="28">
         <f>L27+L34+L38</f>
         <v/>
       </c>
-      <c r="M40" s="27">
+      <c r="M40" s="28">
         <f>M27+M34+M38</f>
         <v/>
       </c>
-      <c r="N40" s="27">
+      <c r="N40" s="28">
         <f>N27+N34+N38</f>
         <v/>
       </c>
-      <c r="O40" s="27">
+      <c r="O40" s="28">
         <f>O27+O34+O38</f>
         <v/>
       </c>
-      <c r="P40" s="27">
+      <c r="P40" s="28">
         <f>P27+P34+P38</f>
         <v/>
       </c>
-      <c r="Q40" s="27">
+      <c r="Q40" s="28">
         <f>Q27+Q34+Q38</f>
         <v/>
       </c>
-      <c r="R40" s="27">
+      <c r="R40" s="28">
         <f>R27+R34+R38</f>
         <v/>
       </c>
-      <c r="S40" s="27">
+      <c r="S40" s="28">
         <f>S27+S34+S38</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>ПЛАНИРОВАНИЕ</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>Юр. лицо</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>Чел.</t>
         </is>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>Месячный фонд</t>
         </is>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D43" s="30" t="inlineStr">
         <is>
           <t>На 6 мес.</t>
         </is>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="30" t="inlineStr">
         <is>
           <t>На 12 мес.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t>БВ</t>
         </is>
       </c>
-      <c r="B44" s="31" t="n">
+      <c r="B44" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <f>S27*1</f>
         <v/>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <f>S27*6</f>
         <v/>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <f>S27*12</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t>АС</t>
         </is>
       </c>
-      <c r="B45" s="31" t="n">
+      <c r="B45" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <f>S34*1</f>
         <v/>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <f>S34*6</f>
         <v/>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <f>S34*12</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t>ИП МТ</t>
         </is>
       </c>
-      <c r="B46" s="31" t="n">
+      <c r="B46" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="33">
         <f>S38*1</f>
         <v/>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="33">
         <f>S38*6</f>
         <v/>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="33">
         <f>S38*12</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B47" s="34" t="n">
+      <c r="B47" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="C47" s="35">
+      <c r="C47" s="36">
         <f>S40*1</f>
         <v/>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="36">
         <f>S40*6</f>
         <v/>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="36">
         <f>S40*12</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
@@ -2790,28 +2857,28 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>4. Среднемесячная выплата 2026 = «Итого 2026» ÷ C5. Это фактический месячный run-rate по начислениям декабрь 2025 – июнь 2026.</t>
+          <t>4. Среднемес. «на руки» 2026 = «Итого 2026» ÷ C5 × (1 − ставка НПД). В исходнике «Итого к выплате» = «на руки» ÷ (1 − ставка), проверено: 236 756 ÷ 0,94 = 251 868.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>5. ВАЖНО: базовая сумма — «Итого к выплате», она УЖЕ включает НПД. Столбец «С НПД +6%» начисляет налог поверх этой суммы. Если нужен НПД на сумму «на руки», базу надо заменить.</t>
+          <t>5. База расчёта — сумма «на руки» (без НПД). Столбцы 2022–2026 и «Итого 2022–2026» остались в «Итого к выплате» — это данные исходника.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>6. Все три надбавки считаются от среднемесячной выплаты: комиссия 4dev = ×3%; сбор ЮЛ Сингапура = ÷0,975 − среднемесячная (2,5% сверху); НПД = ×6%.</t>
+          <t>6. Надбавки от «на руки»: комиссия 4dev = ×3%; сбор ЮЛ Сингапура = ÷0,975 − база; НПД = ÷(1 − ставка) − база, т.е. так же, как считает исходный файл.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>7. «ИТОГО к оплате в месяц» = среднемесячная + комиссия + сбор + НПД (надбавки не каскадируются). Если применять их последовательно (÷0,975 × 1,06 × 1,03), итог по группе будет 3 830 014 ₽ вместо 3 815 806 ₽.</t>
+          <t>7. «ИТОГО к оплате в месяц» = на руки + комиссия + сбор + НПД (надбавки не каскадируются). Столбец T — ставка НПД по каждому человеку (у Абдуллиной 0%).</t>
         </is>
       </c>
     </row>
